--- a/tutorials/DAY 1/assets/lci-carbon-fiber.xlsx
+++ b/tutorials/DAY 1/assets/lci-carbon-fiber.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/GitHub/barcelona-regionalized-lcia/tutorials/DAY 1/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A8BC8BE-E609-1F49-89AA-4648B0E46C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15167813-BDB2-1245-829C-C53701A0DD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4420" yWindow="660" windowWidth="25820" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="660" windowWidth="25820" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Carbon fiber" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="93">
   <si>
     <t>database</t>
   </si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t>carbon fibre, relaxed</t>
+  </si>
+  <si>
+    <t>gas_use*36</t>
   </si>
 </sst>
 </file>
@@ -4808,7 +4811,7 @@
         <v>0.47095746419981693</v>
       </c>
       <c r="T145" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
     </row>
     <row r="146" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
